--- a/src/assets/upload/Arquivo_ Carga_Limites.xlsx
+++ b/src/assets/upload/Arquivo_ Carga_Limites.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F723401\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistemas\SIGVC-FRONTEND\src\assets\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84AA7562-1CFB-44E5-9D0D-85FFDA462F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92398CED-2AD6-4B98-9BEE-018F751020F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{19B5A583-05C6-43C2-94B4-2D63C5F82F2D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{19B5A583-05C6-43C2-94B4-2D63C5F82F2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Upload" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Rubrica</t>
   </si>
@@ -45,6 +45,12 @@
   </si>
   <si>
     <t>Valor Limite</t>
+  </si>
+  <si>
+    <t>3103-04</t>
+  </si>
+  <si>
+    <t>GEAUS</t>
   </si>
 </sst>
 </file>
@@ -426,14 +432,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE34538-ADF3-41C8-9043-46D1EBE920B2}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -444,7 +450,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F7" s="1"/>
     </row>
   </sheetData>
